--- a/data/trans_orig/P37A$vacunaempresa-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P37A$vacunaempresa-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8603</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,82 +748,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4807</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10539</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,35%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5385</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4807</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1835</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>10590</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>263963</t>
+          <t>264407</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272064</t>
+          <t>272103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,82 +861,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>259768</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>255529</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>260838</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>99,59%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>97,96%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>529041</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>523309</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>531988</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>98,03%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>259768</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>255453</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>260838</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>529041</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>523258</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>532013</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>98,02%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8486</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>974</t>
+          <t>980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9559</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>487744</t>
+          <t>487215</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>495463</t>
+          <t>495990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>503055</t>
+          <t>503052</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>987465</t>
+          <t>987889</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>996050</t>
+          <t>996044</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11478</t>
+          <t>11955</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310995</t>
+          <t>311440</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327616</t>
+          <t>326914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>334512</t>
+          <t>334505</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642780</t>
+          <t>642303</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652313</t>
+          <t>652341</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11869</t>
+          <t>13551</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8652</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3504</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16847</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346802</t>
+          <t>345120</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356918</t>
+          <t>356919</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362804</t>
+          <t>362780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370515</t>
+          <t>370514</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713280</t>
+          <t>714120</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>727244</t>
+          <t>726623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>11110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6832</t>
+          <t>6125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13644</t>
+          <t>13425</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>191575</t>
+          <t>192198</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201775</t>
+          <t>202327</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>200836</t>
+          <t>201543</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>397332</t>
+          <t>397551</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>408385</t>
+          <t>409032</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10117</t>
+          <t>9649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261178</t>
+          <t>261312</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538838</t>
+          <t>539306</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12905</t>
+          <t>12980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11487</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19347</t>
+          <t>19939</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602122</t>
+          <t>602047</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>612173</t>
+          <t>612348</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626732</t>
+          <t>627287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>636317</t>
+          <t>636297</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1233899</t>
+          <t>1233307</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1247375</t>
+          <t>1246598</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>18545</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>19804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>726092</t>
+          <t>725250</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>738231</t>
+          <t>738133</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>777724</t>
+          <t>775925</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1507651</t>
+          <t>1507502</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1520979</t>
+          <t>1520974</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48014</t>
+          <t>48567</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>10996</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>28389</t>
+          <t>28172</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>39214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>66045</t>
+          <t>68139</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3228529</t>
+          <t>3227976</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3252273</t>
+          <t>3251959</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3350808</t>
+          <t>3351025</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3367600</t>
+          <t>3368201</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6589696</t>
+          <t>6587602</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6616458</t>
+          <t>6616527</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1702</t>
+          <t>1657</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>11914</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17368</t>
+          <t>18476</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282889</t>
+          <t>281539</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>293036</t>
+          <t>293081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273938</t>
+          <t>275331</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286256</t>
+          <t>286269</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564615</t>
+          <t>563507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>578357</t>
+          <t>578284</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2521</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>18094</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10193</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4206</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21231</t>
+          <t>20529</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488754</t>
+          <t>487433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>503006</t>
+          <t>502892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513572</t>
+          <t>514492</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1008061</t>
+          <t>1008763</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1025086</t>
+          <t>1025112</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7363</t>
+          <t>6399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15140</t>
+          <t>14838</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310531</t>
+          <t>310879</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321229</t>
+          <t>321218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333657</t>
+          <t>334621</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649926</t>
+          <t>650228</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661334</t>
+          <t>661333</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>11016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13936</t>
+          <t>13847</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20860</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>363019</t>
+          <t>362966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>372058</t>
+          <t>372095</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>375015</t>
+          <t>375104</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>386904</t>
+          <t>386216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>742073</t>
+          <t>742399</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>757048</t>
+          <t>756957</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7777</t>
+          <t>6940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14608</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>200513</t>
+          <t>200764</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211601</t>
+          <t>211609</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211814</t>
+          <t>212651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218695</t>
+          <t>218708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>417601</t>
+          <t>416671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>429291</t>
+          <t>429333</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14208</t>
+          <t>13244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>15508</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>259773</t>
+          <t>260737</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>272906</t>
+          <t>272914</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>272778</t>
+          <t>272824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538528</t>
+          <t>538504</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551839</t>
+          <t>551093</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2648</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11370</t>
+          <t>11968</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3780</t>
+          <t>3740</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14841</t>
+          <t>14991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>651418</t>
+          <t>650820</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>660140</t>
+          <t>660850</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>686010</t>
+          <t>686127</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>692914</t>
+          <t>692911</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1341800</t>
+          <t>1341650</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1352861</t>
+          <t>1352901</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16076</t>
+          <t>15870</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>3869</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16956</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>9167</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27554</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>763022</t>
+          <t>763228</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>775323</t>
+          <t>775222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>806897</t>
+          <t>807604</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>819880</t>
+          <t>819984</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1575397</t>
+          <t>1576245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1593706</t>
+          <t>1593784</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34617</t>
+          <t>34748</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>64547</t>
+          <t>64513</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>21545</t>
+          <t>20789</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>43891</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>60565</t>
+          <t>61116</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>98393</t>
+          <t>100264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3362232</t>
+          <t>3362266</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3392162</t>
+          <t>3392031</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3514418</t>
+          <t>3513753</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3536764</t>
+          <t>3537520</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6886695</t>
+          <t>6884824</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6924523</t>
+          <t>6923972</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>6881</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>875</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288429</t>
+          <t>286880</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>282174</t>
+          <t>282184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>573739</t>
+          <t>574625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>581584</t>
+          <t>581589</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>8184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9947</t>
+          <t>9721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3157</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14454</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>493334</t>
+          <t>494391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501553</t>
+          <t>501561</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>513137</t>
+          <t>513363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521991</t>
+          <t>522092</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1011205</t>
+          <t>1011151</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1022600</t>
+          <t>1022502</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>833</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>310347</t>
+          <t>310429</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>329147</t>
+          <t>329148</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336309</t>
+          <t>335476</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643308</t>
+          <t>643006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653244</t>
+          <t>653221</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1731</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13750</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7768</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>1954</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356214</t>
+          <t>357795</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368233</t>
+          <t>368979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>379515</t>
+          <t>378448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>743272</t>
+          <t>742390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>755330</t>
+          <t>755293</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>7866</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>8732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>203196</t>
+          <t>203355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>210264</t>
+          <t>210266</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421978</t>
+          <t>421076</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4598</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>268517</t>
+          <t>268936</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>532288</t>
+          <t>531375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8812</t>
+          <t>7947</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9457,7 +9457,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>11161</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>647746</t>
+          <t>648611</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>682011</t>
+          <t>680133</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1335850</t>
+          <t>1335424</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1346679</t>
+          <t>1346684</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1962</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11280</t>
+          <t>11146</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>814979</t>
+          <t>815155</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>824211</t>
+          <t>824201</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1593470</t>
+          <t>1593604</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1602796</t>
+          <t>1602788</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26472</t>
+          <t>25994</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29907</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>23057</t>
+          <t>23846</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>49113</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3367878</t>
+          <t>3368356</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3385308</t>
+          <t>3385464</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3514635</t>
+          <t>3515659</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3532727</t>
+          <t>3533076</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6890955</t>
+          <t>6889779</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6915835</t>
+          <t>6915046</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13017</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24964</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15798</t>
+          <t>15062</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10088</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25532</t>
+          <t>23192</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28814</t>
+          <t>25543</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19036</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44677</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>298426</t>
+          <t>308364</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>286479</t>
+          <t>299065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>305511</t>
+          <t>313741</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>273837</t>
+          <t>300999</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>264103</t>
+          <t>292869</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>279547</t>
+          <t>306259</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>572263</t>
+          <t>609363</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>556400</t>
+          <t>599097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>582041</t>
+          <t>617591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13193</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,22 +11110,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>12216</t>
+          <t>12213</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22871</t>
+          <t>21758</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -11135,7 +11135,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>513062</t>
+          <t>525371</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505197</t>
+          <t>518091</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>517016</t>
+          <t>529356</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>508081</t>
+          <t>539558</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500287</t>
+          <t>531781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511800</t>
+          <t>543511</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,27 +11223,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1021143</t>
+          <t>1064928</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010488</t>
+          <t>1055383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1027281</t>
+          <t>1070831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,22 +11383,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>757</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6809</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21038</t>
+          <t>21463</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30414</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>24154</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>34346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -11496,27 +11496,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>313341</t>
+          <t>313302</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>309241</t>
+          <t>308278</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315293</t>
+          <t>315228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>328090</t>
+          <t>334918</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318714</t>
+          <t>325979</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335055</t>
+          <t>341698</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>641431</t>
+          <t>648221</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629790</t>
+          <t>638029</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>649206</t>
+          <t>656144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6281</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2282</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11476</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21488</t>
+          <t>21817</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10474</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29553</t>
+          <t>30140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>306437</t>
+          <t>366864</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>298920</t>
+          <t>358140</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310275</t>
+          <t>370958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>464242</t>
+          <t>409613</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>454230</t>
+          <t>400144</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>469991</t>
+          <t>415114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>770678</t>
+          <t>776478</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>758721</t>
+          <t>764967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>777800</t>
+          <t>784135</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3880</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1623</t>
+          <t>1705</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>456</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>9421</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>6092</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>170944</t>
+          <t>197240</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>164679</t>
+          <t>191157</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>174862</t>
+          <t>201302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>257156</t>
+          <t>227213</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>254389</t>
+          <t>224702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>258392</t>
+          <t>228462</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>428100</t>
+          <t>424452</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>421698</t>
+          <t>417790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>432342</t>
+          <t>428490</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2633</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>6734</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8534</t>
+          <t>8462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>20707</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16367</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24897</t>
+          <t>23225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>267003</t>
+          <t>268175</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>261791</t>
+          <t>263973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>268780</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>243323</t>
+          <t>250442</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235597</t>
+          <t>243043</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>248522</t>
+          <t>255288</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>510325</t>
+          <t>518616</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>501795</t>
+          <t>511232</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516387</t>
+          <t>524389</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29326</t>
+          <t>32454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>31396</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>21658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39713</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>45452</t>
+          <t>51745</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>28307</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>61912</t>
+          <t>65860</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>605619</t>
+          <t>699338</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>594953</t>
+          <t>687233</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613822</t>
+          <t>707937</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>822473</t>
+          <t>740661</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>809552</t>
+          <t>729291</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>836782</t>
+          <t>750399</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1428092</t>
+          <t>1439999</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1411632</t>
+          <t>1425884</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1445237</t>
+          <t>1453317</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>33818</t>
+          <t>38771</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15476</t>
+          <t>28132</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51801</t>
+          <t>51686</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>13580</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20880</t>
+          <t>22439</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>47397</t>
+          <t>53954</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28879</t>
+          <t>41660</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63934</t>
+          <t>70194</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>894902</t>
+          <t>759301</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>876919</t>
+          <t>746386</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>913244</t>
+          <t>769940</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>704151</t>
+          <t>816148</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>696851</t>
+          <t>808892</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>709137</t>
+          <t>821698</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1599055</t>
+          <t>1575449</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1582518</t>
+          <t>1559209</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1617573</t>
+          <t>1587743</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>90082</t>
+          <t>94807</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67409</t>
+          <t>77178</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>110563</t>
+          <t>116429</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>110929</t>
+          <t>117402</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>86964</t>
+          <t>100735</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>131265</t>
+          <t>139588</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>201011</t>
+          <t>212209</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>170575</t>
+          <t>187093</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>235060</t>
+          <t>245828</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3369735</t>
+          <t>3437955</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3349254</t>
+          <t>3416333</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3392408</t>
+          <t>3455584</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3601351</t>
+          <t>3619552</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3581015</t>
+          <t>3597366</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3625316</t>
+          <t>3636219</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6971086</t>
+          <t>7057507</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6937037</t>
+          <t>7023888</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7001522</t>
+          <t>7082623</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
